--- a/data/monthly/【2026年4月】月次数値.xlsx
+++ b/data/monthly/【2026年4月】月次数値.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="600" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="163">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -371,31 +370,168 @@
   </si>
   <si>
     <t>こんどう内科クリニック</t>
+  </si>
+  <si>
+    <t>鍼灸サロンNOA</t>
+  </si>
+  <si>
+    <t>有限会社 ムネケン</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>堀田歯科</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>整体処 たくみ堂</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>金町駅前ジャスミン歯科（2回目）</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>掛川整体院サウレ</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>すがや歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>スカイハイ英語塾</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>アキュラデンタルクリニック</t>
+  </si>
+  <si>
+    <t>UESUGI美容鍼灸整骨院</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>PML　広尾店</t>
+  </si>
+  <si>
+    <t>Healing Salon Ange</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>DesignBody 御徒町店</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>Beauty Salon Arona</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -403,36 +539,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -721,14 +857,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:Y58"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y89"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -805,7 +938,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -831,10 +964,10 @@
         <v>2127</v>
       </c>
       <c r="I2">
-        <v>1.51622</v>
+        <v>1.5162199999999999</v>
       </c>
       <c r="J2">
-        <v>43.11818182</v>
+        <v>43.118181819999997</v>
       </c>
       <c r="K2">
         <v>320</v>
@@ -858,28 +991,28 @@
         <v>110</v>
       </c>
       <c r="S2">
-        <v>43.118182</v>
+        <v>43.118181999999997</v>
       </c>
       <c r="T2">
-        <v>3.410853</v>
+        <v>3.4108529999999999</v>
       </c>
       <c r="U2">
         <v>118</v>
       </c>
       <c r="V2">
-        <v>3.658915</v>
+        <v>3.6589149999999999</v>
       </c>
       <c r="W2">
-        <v>40.194915</v>
+        <v>40.194915000000002</v>
       </c>
       <c r="X2">
         <v>55</v>
       </c>
       <c r="Y2">
-        <v>86.236364</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
+        <v>86.236363999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -905,10 +1038,10 @@
         <v>1857</v>
       </c>
       <c r="I3">
-        <v>1.499192</v>
+        <v>1.4991920000000001</v>
       </c>
       <c r="J3">
-        <v>39.83050847</v>
+        <v>39.830508469999998</v>
       </c>
       <c r="K3">
         <v>160</v>
@@ -926,34 +1059,34 @@
         <v>2784</v>
       </c>
       <c r="P3">
-        <v>1688.218391</v>
+        <v>1688.2183910000001</v>
       </c>
       <c r="Q3">
         <v>118</v>
       </c>
       <c r="S3">
-        <v>39.830508</v>
+        <v>39.830508000000002</v>
       </c>
       <c r="T3">
-        <v>4.238506</v>
+        <v>4.2385060000000001</v>
       </c>
       <c r="U3">
         <v>115</v>
       </c>
       <c r="V3">
-        <v>4.130747</v>
+        <v>4.1307470000000004</v>
       </c>
       <c r="W3">
-        <v>40.869565</v>
+        <v>40.869565000000001</v>
       </c>
       <c r="X3">
         <v>71</v>
       </c>
       <c r="Y3">
-        <v>66.197183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
+        <v>66.197182999999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -979,10 +1112,10 @@
         <v>2504</v>
       </c>
       <c r="I4">
-        <v>1.368211</v>
+        <v>1.3682110000000001</v>
       </c>
       <c r="J4">
-        <v>48.24242424</v>
+        <v>48.242424239999998</v>
       </c>
       <c r="K4">
         <v>160</v>
@@ -1000,7 +1133,7 @@
         <v>3426</v>
       </c>
       <c r="P4">
-        <v>1394.045534</v>
+        <v>1394.0455340000001</v>
       </c>
       <c r="Q4">
         <v>99</v>
@@ -1009,13 +1142,13 @@
         <v>48.242424</v>
       </c>
       <c r="T4">
-        <v>2.889667</v>
+        <v>2.8896670000000002</v>
       </c>
       <c r="U4">
         <v>99</v>
       </c>
       <c r="V4">
-        <v>2.889667</v>
+        <v>2.8896670000000002</v>
       </c>
       <c r="W4">
         <v>48.242424</v>
@@ -1024,10 +1157,10 @@
         <v>56</v>
       </c>
       <c r="Y4">
-        <v>85.285714</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+        <v>85.285713999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1053,10 +1186,10 @@
         <v>2577</v>
       </c>
       <c r="I5">
-        <v>1.538223</v>
+        <v>1.5382229999999999</v>
       </c>
       <c r="J5">
-        <v>42.65765766</v>
+        <v>42.657657659999998</v>
       </c>
       <c r="K5">
         <v>160</v>
@@ -1080,10 +1213,10 @@
         <v>111</v>
       </c>
       <c r="S5">
-        <v>42.657658</v>
+        <v>42.657657999999998</v>
       </c>
       <c r="T5">
-        <v>2.800202</v>
+        <v>2.8002020000000001</v>
       </c>
       <c r="U5">
         <v>118</v>
@@ -1101,7 +1234,7 @@
         <v>73.984375</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1130,7 +1263,7 @@
         <v>1.805693</v>
       </c>
       <c r="J6">
-        <v>60.97435897</v>
+        <v>60.974358969999997</v>
       </c>
       <c r="K6">
         <v>160</v>
@@ -1157,7 +1290,7 @@
         <v>60.974359</v>
       </c>
       <c r="T6">
-        <v>1.782042</v>
+        <v>1.7820419999999999</v>
       </c>
       <c r="U6">
         <v>82</v>
@@ -1175,7 +1308,7 @@
         <v>101.191489</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1204,7 +1337,7 @@
         <v>1.334193</v>
       </c>
       <c r="J7">
-        <v>24.33333333</v>
+        <v>24.333333329999999</v>
       </c>
       <c r="K7">
         <v>160</v>
@@ -1231,25 +1364,25 @@
         <v>24.333333</v>
       </c>
       <c r="T7">
-        <v>4.710145</v>
+        <v>4.7101449999999998</v>
       </c>
       <c r="U7">
         <v>204</v>
       </c>
       <c r="V7">
-        <v>4.927536</v>
+        <v>4.9275359999999999</v>
       </c>
       <c r="W7">
-        <v>23.259804</v>
+        <v>23.259803999999999</v>
       </c>
       <c r="X7">
         <v>105</v>
       </c>
       <c r="Y7">
-        <v>45.190476</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>45.190475999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1278,7 +1411,7 @@
         <v>1.338303</v>
       </c>
       <c r="J8">
-        <v>21.34684685</v>
+        <v>21.346846849999999</v>
       </c>
       <c r="K8">
         <v>160</v>
@@ -1305,25 +1438,25 @@
         <v>21.346847</v>
       </c>
       <c r="T8">
-        <v>4.755784</v>
+        <v>4.7557840000000002</v>
       </c>
       <c r="U8">
         <v>219</v>
       </c>
       <c r="V8">
-        <v>4.691517</v>
+        <v>4.6915170000000002</v>
       </c>
       <c r="W8">
-        <v>21.639269</v>
+        <v>21.639268999999999</v>
       </c>
       <c r="X8">
         <v>114</v>
       </c>
       <c r="Y8">
-        <v>41.570175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+        <v>41.570174999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1349,7 +1482,7 @@
         <v>5133</v>
       </c>
       <c r="I9">
-        <v>1.222287</v>
+        <v>1.2222869999999999</v>
       </c>
       <c r="J9">
         <v>30.72839506</v>
@@ -1370,34 +1503,34 @@
         <v>6274</v>
       </c>
       <c r="P9">
-        <v>793.433216</v>
+        <v>793.43321600000002</v>
       </c>
       <c r="Q9">
         <v>261</v>
       </c>
       <c r="S9">
-        <v>19.072797</v>
+        <v>19.072797000000001</v>
       </c>
       <c r="T9">
-        <v>4.160026</v>
+        <v>4.1600260000000002</v>
       </c>
       <c r="U9">
         <v>293</v>
       </c>
       <c r="V9">
-        <v>4.670067</v>
+        <v>4.6700670000000004</v>
       </c>
       <c r="W9">
-        <v>16.989761</v>
+        <v>16.989761000000001</v>
       </c>
       <c r="X9">
         <v>162</v>
       </c>
       <c r="Y9">
-        <v>30.728395</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+        <v>30.728394999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1423,7 +1556,7 @@
         <v>2079</v>
       </c>
       <c r="I10">
-        <v>1.505532</v>
+        <v>1.5055320000000001</v>
       </c>
       <c r="J10">
         <v>56.27906977</v>
@@ -1450,10 +1583,10 @@
         <v>108</v>
       </c>
       <c r="S10">
-        <v>44.814815</v>
+        <v>44.814815000000003</v>
       </c>
       <c r="T10">
-        <v>3.450479</v>
+        <v>3.4504790000000001</v>
       </c>
       <c r="U10">
         <v>116</v>
@@ -1462,16 +1595,16 @@
         <v>3.70607</v>
       </c>
       <c r="W10">
-        <v>41.724138</v>
+        <v>41.724138000000004</v>
       </c>
       <c r="X10">
         <v>86</v>
       </c>
       <c r="Y10">
-        <v>56.27907</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>56.279069999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1497,10 +1630,10 @@
         <v>3006</v>
       </c>
       <c r="I11">
-        <v>1.387558</v>
+        <v>1.3875580000000001</v>
       </c>
       <c r="J11">
-        <v>63.48192771</v>
+        <v>63.481927710000001</v>
       </c>
       <c r="K11" t="s">
         <v>42</v>
@@ -1524,7 +1657,7 @@
         <v>125</v>
       </c>
       <c r="S11">
-        <v>42.152</v>
+        <v>42.152000000000001</v>
       </c>
       <c r="T11">
         <v>2.996883</v>
@@ -1536,16 +1669,16 @@
         <v>3.236634</v>
       </c>
       <c r="W11">
-        <v>39.02963</v>
+        <v>39.029629999999997</v>
       </c>
       <c r="X11">
         <v>83</v>
       </c>
       <c r="Y11">
-        <v>63.481928</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+        <v>63.481928000000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1574,7 +1707,7 @@
         <v>1.385839</v>
       </c>
       <c r="J12">
-        <v>49.85981308</v>
+        <v>49.859813080000002</v>
       </c>
       <c r="K12" t="s">
         <v>42</v>
@@ -1601,7 +1734,7 @@
         <v>42.68</v>
       </c>
       <c r="T12">
-        <v>2.813414</v>
+        <v>2.8134139999999999</v>
       </c>
       <c r="U12">
         <v>140</v>
@@ -1610,16 +1743,16 @@
         <v>3.151024</v>
       </c>
       <c r="W12">
-        <v>38.107143</v>
+        <v>38.107143000000001</v>
       </c>
       <c r="X12">
         <v>107</v>
       </c>
       <c r="Y12">
-        <v>49.859813</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+        <v>49.859813000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1648,7 +1781,7 @@
         <v>1.172569</v>
       </c>
       <c r="J13">
-        <v>65.79545455</v>
+        <v>65.795454550000002</v>
       </c>
       <c r="K13" t="s">
         <v>42</v>
@@ -1672,7 +1805,7 @@
         <v>93</v>
       </c>
       <c r="S13">
-        <v>62.258065</v>
+        <v>62.258065000000002</v>
       </c>
       <c r="T13">
         <v>2.753924</v>
@@ -1681,7 +1814,7 @@
         <v>107</v>
       </c>
       <c r="V13">
-        <v>3.168493</v>
+        <v>3.1684929999999998</v>
       </c>
       <c r="W13">
         <v>54.11215</v>
@@ -1690,10 +1823,10 @@
         <v>88</v>
       </c>
       <c r="Y13">
-        <v>65.795455</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+        <v>65.795455000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1719,7 +1852,7 @@
         <v>2811</v>
       </c>
       <c r="I14">
-        <v>1.283173</v>
+        <v>1.2831729999999999</v>
       </c>
       <c r="J14">
         <v>65.9375</v>
@@ -1746,19 +1879,19 @@
         <v>136</v>
       </c>
       <c r="S14">
-        <v>38.786765</v>
+        <v>38.786765000000003</v>
       </c>
       <c r="T14">
-        <v>3.770446</v>
+        <v>3.7704460000000002</v>
       </c>
       <c r="U14">
         <v>142</v>
       </c>
       <c r="V14">
-        <v>3.93679</v>
+        <v>3.9367899999999998</v>
       </c>
       <c r="W14">
-        <v>37.147887</v>
+        <v>37.147886999999997</v>
       </c>
       <c r="X14">
         <v>80</v>
@@ -1767,7 +1900,7 @@
         <v>65.9375</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1796,7 +1929,7 @@
         <v>1.343874</v>
       </c>
       <c r="J15">
-        <v>50.07407407</v>
+        <v>50.074074070000002</v>
       </c>
       <c r="K15" t="s">
         <v>42</v>
@@ -1814,13 +1947,13 @@
         <v>4420</v>
       </c>
       <c r="P15">
-        <v>1223.529412</v>
+        <v>1223.5294120000001</v>
       </c>
       <c r="Q15">
         <v>118</v>
       </c>
       <c r="S15">
-        <v>45.830508</v>
+        <v>45.830508000000002</v>
       </c>
       <c r="T15">
         <v>2.669683</v>
@@ -1832,16 +1965,16 @@
         <v>2.850679</v>
       </c>
       <c r="W15">
-        <v>42.920635</v>
+        <v>42.920634999999997</v>
       </c>
       <c r="X15">
         <v>108</v>
       </c>
       <c r="Y15">
-        <v>50.074074</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+        <v>50.074074000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1870,7 +2003,7 @@
         <v>1.506311</v>
       </c>
       <c r="J16">
-        <v>45.76271186</v>
+        <v>45.762711860000003</v>
       </c>
       <c r="K16" t="s">
         <v>42</v>
@@ -1894,16 +2027,16 @@
         <v>183</v>
       </c>
       <c r="S16">
-        <v>29.508197</v>
+        <v>29.508196999999999</v>
       </c>
       <c r="T16">
-        <v>3.565861</v>
+        <v>3.5658609999999999</v>
       </c>
       <c r="U16">
         <v>216</v>
       </c>
       <c r="V16">
-        <v>4.208885</v>
+        <v>4.2088850000000004</v>
       </c>
       <c r="W16">
         <v>25</v>
@@ -1912,10 +2045,10 @@
         <v>118</v>
       </c>
       <c r="Y16">
-        <v>45.762712</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
+        <v>45.762712000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1944,7 +2077,7 @@
         <v>1.545857</v>
       </c>
       <c r="J17">
-        <v>35.60273973</v>
+        <v>35.602739730000003</v>
       </c>
       <c r="K17" t="s">
         <v>42</v>
@@ -1962,7 +2095,7 @@
         <v>5242</v>
       </c>
       <c r="P17">
-        <v>991.606257</v>
+        <v>991.60625700000003</v>
       </c>
       <c r="Q17">
         <v>226</v>
@@ -1971,13 +2104,13 @@
         <v>23</v>
       </c>
       <c r="T17">
-        <v>4.311332</v>
+        <v>4.3113320000000002</v>
       </c>
       <c r="U17">
         <v>237</v>
       </c>
       <c r="V17">
-        <v>4.521175</v>
+        <v>4.5211750000000004</v>
       </c>
       <c r="W17">
         <v>21.932489</v>
@@ -1986,10 +2119,10 @@
         <v>146</v>
       </c>
       <c r="Y17">
-        <v>35.60274</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>35.602739999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -2018,7 +2151,7 @@
         <v>1.340368</v>
       </c>
       <c r="J18">
-        <v>64.17647059</v>
+        <v>64.176470589999994</v>
       </c>
       <c r="K18" t="s">
         <v>42</v>
@@ -2042,16 +2175,16 @@
         <v>119</v>
       </c>
       <c r="S18">
-        <v>45.840336</v>
+        <v>45.840336000000001</v>
       </c>
       <c r="T18">
-        <v>2.402099</v>
+        <v>2.4020990000000002</v>
       </c>
       <c r="U18">
         <v>137</v>
       </c>
       <c r="V18">
-        <v>2.765442</v>
+        <v>2.7654420000000002</v>
       </c>
       <c r="W18">
         <v>39.817518</v>
@@ -2060,10 +2193,10 @@
         <v>85</v>
       </c>
       <c r="Y18">
-        <v>64.176471</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25">
+        <v>64.176471000000006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -2089,7 +2222,7 @@
         <v>2444</v>
       </c>
       <c r="I19">
-        <v>1.779869</v>
+        <v>1.7798689999999999</v>
       </c>
       <c r="J19">
         <v>102.35849057</v>
@@ -2110,22 +2243,22 @@
         <v>4350</v>
       </c>
       <c r="P19">
-        <v>1247.126437</v>
+        <v>1247.1264369999999</v>
       </c>
       <c r="Q19">
         <v>63</v>
       </c>
       <c r="S19">
-        <v>86.111111</v>
+        <v>86.111110999999994</v>
       </c>
       <c r="T19">
-        <v>1.448276</v>
+        <v>1.4482759999999999</v>
       </c>
       <c r="U19">
         <v>70</v>
       </c>
       <c r="V19">
-        <v>1.609195</v>
+        <v>1.6091949999999999</v>
       </c>
       <c r="W19">
         <v>77.5</v>
@@ -2137,7 +2270,7 @@
         <v>102.358491</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2166,7 +2299,7 @@
         <v>1.585032</v>
       </c>
       <c r="J20">
-        <v>67.15384615</v>
+        <v>67.153846150000007</v>
       </c>
       <c r="K20" t="s">
         <v>42</v>
@@ -2184,16 +2317,16 @@
         <v>4977</v>
       </c>
       <c r="P20">
-        <v>1052.44123</v>
+        <v>1052.4412299999999</v>
       </c>
       <c r="Q20">
         <v>112</v>
       </c>
       <c r="S20">
-        <v>46.767857</v>
+        <v>46.767856999999999</v>
       </c>
       <c r="T20">
-        <v>2.250352</v>
+        <v>2.2503519999999999</v>
       </c>
       <c r="U20">
         <v>123</v>
@@ -2208,10 +2341,10 @@
         <v>78</v>
       </c>
       <c r="Y20">
-        <v>67.153846</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
+        <v>67.153846000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2237,10 +2370,10 @@
         <v>2444</v>
       </c>
       <c r="I21">
-        <v>1.359247</v>
+        <v>1.3592470000000001</v>
       </c>
       <c r="J21">
-        <v>38.82142857</v>
+        <v>38.821428570000002</v>
       </c>
       <c r="K21" t="s">
         <v>42</v>
@@ -2258,22 +2391,22 @@
         <v>3322</v>
       </c>
       <c r="P21">
-        <v>1636.062613</v>
+        <v>1636.0626130000001</v>
       </c>
       <c r="Q21">
         <v>178</v>
       </c>
       <c r="S21">
-        <v>30.533708</v>
+        <v>30.533708000000001</v>
       </c>
       <c r="T21">
-        <v>5.358218</v>
+        <v>5.3582179999999999</v>
       </c>
       <c r="U21">
         <v>192</v>
       </c>
       <c r="V21">
-        <v>5.779651</v>
+        <v>5.7796510000000003</v>
       </c>
       <c r="W21">
         <v>28.307292</v>
@@ -2282,10 +2415,10 @@
         <v>140</v>
       </c>
       <c r="Y21">
-        <v>38.821429</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+        <v>38.821429000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -2314,7 +2447,7 @@
         <v>1.592568</v>
       </c>
       <c r="J22">
-        <v>71.41772152</v>
+        <v>71.417721520000001</v>
       </c>
       <c r="K22" t="s">
         <v>42</v>
@@ -2341,25 +2474,25 @@
         <v>59.389474</v>
       </c>
       <c r="T22">
-        <v>1.961594</v>
+        <v>1.9615940000000001</v>
       </c>
       <c r="U22">
         <v>113</v>
       </c>
       <c r="V22">
-        <v>2.333265</v>
+        <v>2.3332649999999999</v>
       </c>
       <c r="W22">
-        <v>49.929204</v>
+        <v>49.929203999999999</v>
       </c>
       <c r="X22">
         <v>79</v>
       </c>
       <c r="Y22">
-        <v>71.417722</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25">
+        <v>71.417721999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2409,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2435,10 +2568,10 @@
         <v>3324</v>
       </c>
       <c r="I24">
-        <v>1.69284</v>
+        <v>1.6928399999999999</v>
       </c>
       <c r="J24">
-        <v>57.41836735</v>
+        <v>57.418367349999997</v>
       </c>
       <c r="K24" t="s">
         <v>42</v>
@@ -2462,28 +2595,28 @@
         <v>148</v>
       </c>
       <c r="S24">
-        <v>38.02027</v>
+        <v>38.020269999999996</v>
       </c>
       <c r="T24">
-        <v>2.630176</v>
+        <v>2.6301760000000001</v>
       </c>
       <c r="U24">
         <v>185</v>
       </c>
       <c r="V24">
-        <v>3.28772</v>
+        <v>3.2877200000000002</v>
       </c>
       <c r="W24">
-        <v>30.416216</v>
+        <v>30.416215999999999</v>
       </c>
       <c r="X24">
         <v>98</v>
       </c>
       <c r="Y24">
-        <v>57.418367</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
+        <v>57.418367000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2512,7 +2645,7 @@
         <v>1.451778</v>
       </c>
       <c r="J25">
-        <v>41.16901408</v>
+        <v>41.169014079999997</v>
       </c>
       <c r="K25" t="s">
         <v>42</v>
@@ -2545,19 +2678,19 @@
         <v>206</v>
       </c>
       <c r="V25">
-        <v>4.036841</v>
+        <v>4.0368409999999999</v>
       </c>
       <c r="W25">
-        <v>28.378641</v>
+        <v>28.378640999999998</v>
       </c>
       <c r="X25">
         <v>142</v>
       </c>
       <c r="Y25">
-        <v>41.169014</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
+        <v>41.169013999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2583,10 +2716,10 @@
         <v>4053</v>
       </c>
       <c r="I26">
-        <v>1.596842</v>
+        <v>1.5968420000000001</v>
       </c>
       <c r="J26">
-        <v>31.73714286</v>
+        <v>31.737142859999999</v>
       </c>
       <c r="K26" t="s">
         <v>42</v>
@@ -2604,25 +2737,25 @@
         <v>6472</v>
       </c>
       <c r="P26">
-        <v>858.15822</v>
+        <v>858.15822000000003</v>
       </c>
       <c r="Q26">
         <v>255</v>
       </c>
       <c r="S26">
-        <v>21.780392</v>
+        <v>21.780391999999999</v>
       </c>
       <c r="T26">
-        <v>3.940049</v>
+        <v>3.9400490000000001</v>
       </c>
       <c r="U26">
         <v>276</v>
       </c>
       <c r="V26">
-        <v>4.264524</v>
+        <v>4.2645239999999998</v>
       </c>
       <c r="W26">
-        <v>20.123188</v>
+        <v>20.123187999999999</v>
       </c>
       <c r="X26">
         <v>175</v>
@@ -2631,7 +2764,7 @@
         <v>31.737143</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2660,7 +2793,7 @@
         <v>1.30301</v>
       </c>
       <c r="J27">
-        <v>57.91509434</v>
+        <v>57.915094340000003</v>
       </c>
       <c r="K27" t="s">
         <v>42</v>
@@ -2684,7 +2817,7 @@
         <v>131</v>
       </c>
       <c r="S27">
-        <v>46.862595</v>
+        <v>46.862594999999999</v>
       </c>
       <c r="T27">
         <v>3.325717</v>
@@ -2696,16 +2829,16 @@
         <v>3.630363</v>
       </c>
       <c r="W27">
-        <v>42.93007</v>
+        <v>42.930070000000001</v>
       </c>
       <c r="X27">
         <v>106</v>
       </c>
       <c r="Y27">
-        <v>57.915094</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25">
+        <v>57.915094000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2752,7 +2885,7 @@
         <v>8336</v>
       </c>
       <c r="P28">
-        <v>634.836852</v>
+        <v>634.83685200000002</v>
       </c>
       <c r="Q28">
         <v>630</v>
@@ -2767,10 +2900,10 @@
         <v>728</v>
       </c>
       <c r="V28">
-        <v>8.733205</v>
+        <v>8.7332049999999999</v>
       </c>
       <c r="W28">
-        <v>7.269231</v>
+        <v>7.2692310000000004</v>
       </c>
       <c r="X28">
         <v>392</v>
@@ -2779,7 +2912,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2808,7 +2941,7 @@
         <v>1.773865</v>
       </c>
       <c r="J29">
-        <v>77.30379747</v>
+        <v>77.303797470000006</v>
       </c>
       <c r="K29" t="s">
         <v>42</v>
@@ -2832,28 +2965,28 @@
         <v>101</v>
       </c>
       <c r="S29">
-        <v>60.465347</v>
+        <v>60.465347000000001</v>
       </c>
       <c r="T29">
-        <v>2.41569</v>
+        <v>2.4156900000000001</v>
       </c>
       <c r="U29">
         <v>113</v>
       </c>
       <c r="V29">
-        <v>2.702703</v>
+        <v>2.7027030000000001</v>
       </c>
       <c r="W29">
-        <v>54.044248</v>
+        <v>54.044248000000003</v>
       </c>
       <c r="X29">
         <v>79</v>
       </c>
       <c r="Y29">
-        <v>77.303797</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25">
+        <v>77.303797000000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2879,10 +3012,10 @@
         <v>2726</v>
       </c>
       <c r="I30">
-        <v>1.423698</v>
+        <v>1.4236979999999999</v>
       </c>
       <c r="J30">
-        <v>67.62626263</v>
+        <v>67.626262629999999</v>
       </c>
       <c r="K30" t="s">
         <v>42</v>
@@ -2909,7 +3042,7 @@
         <v>54.877049</v>
       </c>
       <c r="T30">
-        <v>3.14352</v>
+        <v>3.1435200000000001</v>
       </c>
       <c r="U30">
         <v>136</v>
@@ -2918,16 +3051,16 @@
         <v>3.504251</v>
       </c>
       <c r="W30">
-        <v>49.227941</v>
+        <v>49.227941000000001</v>
       </c>
       <c r="X30">
         <v>99</v>
       </c>
       <c r="Y30">
-        <v>67.626263</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25">
+        <v>67.626262999999994</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -2956,7 +3089,7 @@
         <v>1.724073</v>
       </c>
       <c r="J31">
-        <v>53.05504587</v>
+        <v>53.055045870000001</v>
       </c>
       <c r="K31" t="s">
         <v>42</v>
@@ -2974,13 +3107,13 @@
         <v>5486</v>
       </c>
       <c r="P31">
-        <v>1054.137805</v>
+        <v>1054.1378050000001</v>
       </c>
       <c r="Q31">
         <v>152</v>
       </c>
       <c r="S31">
-        <v>38.046053</v>
+        <v>38.046053000000001</v>
       </c>
       <c r="T31">
         <v>2.770689</v>
@@ -2989,19 +3122,19 @@
         <v>180</v>
       </c>
       <c r="V31">
-        <v>3.281079</v>
+        <v>3.2810790000000001</v>
       </c>
       <c r="W31">
-        <v>32.127778</v>
+        <v>32.127777999999999</v>
       </c>
       <c r="X31">
         <v>109</v>
       </c>
       <c r="Y31">
-        <v>53.055046</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25">
+        <v>53.055045999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -3030,7 +3163,7 @@
         <v>1.487344</v>
       </c>
       <c r="J32">
-        <v>69.48809524</v>
+        <v>69.488095240000007</v>
       </c>
       <c r="K32" t="s">
         <v>42</v>
@@ -3048,34 +3181,34 @@
         <v>5347</v>
       </c>
       <c r="P32">
-        <v>1091.640172</v>
+        <v>1091.6401719999999</v>
       </c>
       <c r="Q32">
         <v>139</v>
       </c>
       <c r="S32">
-        <v>41.992806</v>
+        <v>41.992806000000002</v>
       </c>
       <c r="T32">
-        <v>2.599589</v>
+        <v>2.5995889999999999</v>
       </c>
       <c r="U32">
         <v>175</v>
       </c>
       <c r="V32">
-        <v>3.272863</v>
+        <v>3.2728630000000001</v>
       </c>
       <c r="W32">
-        <v>33.354286</v>
+        <v>33.354286000000002</v>
       </c>
       <c r="X32">
         <v>84</v>
       </c>
       <c r="Y32">
-        <v>69.488095</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25">
+        <v>69.488095000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -3101,10 +3234,10 @@
         <v>3054</v>
       </c>
       <c r="I33">
-        <v>1.212508</v>
+        <v>1.2125079999999999</v>
       </c>
       <c r="J33">
-        <v>72.98863636</v>
+        <v>72.988636360000001</v>
       </c>
       <c r="K33" t="s">
         <v>42</v>
@@ -3128,7 +3261,7 @@
         <v>98</v>
       </c>
       <c r="S33">
-        <v>65.540816</v>
+        <v>65.540816000000007</v>
       </c>
       <c r="T33">
         <v>2.646503</v>
@@ -3137,10 +3270,10 @@
         <v>114</v>
       </c>
       <c r="V33">
-        <v>3.078585</v>
+        <v>3.0785849999999999</v>
       </c>
       <c r="W33">
-        <v>56.342105</v>
+        <v>56.342104999999997</v>
       </c>
       <c r="X33">
         <v>88</v>
@@ -3149,7 +3282,7 @@
         <v>72.988636</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -3175,10 +3308,10 @@
         <v>2811</v>
       </c>
       <c r="I34">
-        <v>1.804696</v>
+        <v>1.8046960000000001</v>
       </c>
       <c r="J34">
-        <v>60.90721649</v>
+        <v>60.907216490000003</v>
       </c>
       <c r="K34" t="s">
         <v>42</v>
@@ -3196,34 +3329,34 @@
         <v>5073</v>
       </c>
       <c r="P34">
-        <v>1164.596885</v>
+        <v>1164.5968849999999</v>
       </c>
       <c r="Q34">
         <v>126</v>
       </c>
       <c r="S34">
-        <v>46.888889</v>
+        <v>46.888888999999999</v>
       </c>
       <c r="T34">
-        <v>2.483737</v>
+        <v>2.4837370000000001</v>
       </c>
       <c r="U34">
         <v>142</v>
       </c>
       <c r="V34">
-        <v>2.799133</v>
+        <v>2.7991329999999999</v>
       </c>
       <c r="W34">
-        <v>41.605634</v>
+        <v>41.605634000000002</v>
       </c>
       <c r="X34">
         <v>97</v>
       </c>
       <c r="Y34">
-        <v>60.907216</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25">
+        <v>60.907215999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -3252,7 +3385,7 @@
         <v>1.531528</v>
       </c>
       <c r="J35">
-        <v>64.58947368</v>
+        <v>64.589473679999998</v>
       </c>
       <c r="K35" t="s">
         <v>42</v>
@@ -3270,13 +3403,13 @@
         <v>4299</v>
       </c>
       <c r="P35">
-        <v>1427.308676</v>
+        <v>1427.3086760000001</v>
       </c>
       <c r="Q35">
         <v>110</v>
       </c>
       <c r="S35">
-        <v>55.781818</v>
+        <v>55.781818000000001</v>
       </c>
       <c r="T35">
         <v>2.558735</v>
@@ -3285,19 +3418,19 @@
         <v>149</v>
       </c>
       <c r="V35">
-        <v>3.465922</v>
+        <v>3.4659219999999999</v>
       </c>
       <c r="W35">
-        <v>41.181208</v>
+        <v>41.181207999999998</v>
       </c>
       <c r="X35">
         <v>95</v>
       </c>
       <c r="Y35">
-        <v>64.589474</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25">
+        <v>64.589473999999996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -3326,7 +3459,7 @@
         <v>1.43452</v>
       </c>
       <c r="J36">
-        <v>25.05504587</v>
+        <v>25.055045870000001</v>
       </c>
       <c r="K36" t="s">
         <v>42</v>
@@ -3344,7 +3477,7 @@
         <v>6649</v>
       </c>
       <c r="P36">
-        <v>821.476914</v>
+        <v>821.47691399999997</v>
       </c>
       <c r="Q36">
         <v>349</v>
@@ -3353,25 +3486,25 @@
         <v>15.65043</v>
       </c>
       <c r="T36">
-        <v>5.24891</v>
+        <v>5.2489100000000004</v>
       </c>
       <c r="U36">
         <v>368</v>
       </c>
       <c r="V36">
-        <v>5.534667</v>
+        <v>5.5346669999999998</v>
       </c>
       <c r="W36">
-        <v>14.842391</v>
+        <v>14.842390999999999</v>
       </c>
       <c r="X36">
         <v>218</v>
       </c>
       <c r="Y36">
-        <v>25.055046</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25">
+        <v>25.055046000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -3418,7 +3551,7 @@
         <v>3609</v>
       </c>
       <c r="P37">
-        <v>1309.226933</v>
+        <v>1309.2269329999999</v>
       </c>
       <c r="Q37">
         <v>112</v>
@@ -3427,16 +3560,16 @@
         <v>42.1875</v>
       </c>
       <c r="T37">
-        <v>3.103353</v>
+        <v>3.1033529999999998</v>
       </c>
       <c r="U37">
         <v>124</v>
       </c>
       <c r="V37">
-        <v>3.435855</v>
+        <v>3.4358550000000001</v>
       </c>
       <c r="W37">
-        <v>38.104839</v>
+        <v>38.104838999999998</v>
       </c>
       <c r="X37">
         <v>80</v>
@@ -3445,7 +3578,7 @@
         <v>59.0625</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -3471,10 +3604,10 @@
         <v>2405</v>
       </c>
       <c r="I38">
-        <v>1.209563</v>
+        <v>1.2095629999999999</v>
       </c>
       <c r="J38">
-        <v>61.76315789</v>
+        <v>61.763157890000002</v>
       </c>
       <c r="K38" t="s">
         <v>42</v>
@@ -3492,34 +3625,34 @@
         <v>2909</v>
       </c>
       <c r="P38">
-        <v>1613.612925</v>
+        <v>1613.6129249999999</v>
       </c>
       <c r="Q38">
         <v>91</v>
       </c>
       <c r="S38">
-        <v>51.582418</v>
+        <v>51.582417999999997</v>
       </c>
       <c r="T38">
-        <v>3.128223</v>
+        <v>3.1282230000000002</v>
       </c>
       <c r="U38">
         <v>102</v>
       </c>
       <c r="V38">
-        <v>3.50636</v>
+        <v>3.5063599999999999</v>
       </c>
       <c r="W38">
-        <v>46.019608</v>
+        <v>46.019607999999998</v>
       </c>
       <c r="X38">
         <v>76</v>
       </c>
       <c r="Y38">
-        <v>61.763158</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25">
+        <v>61.763157999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -3548,7 +3681,7 @@
         <v>1.443346</v>
       </c>
       <c r="J39">
-        <v>54.48275862</v>
+        <v>54.482758619999998</v>
       </c>
       <c r="K39" t="s">
         <v>42</v>
@@ -3572,10 +3705,10 @@
         <v>113</v>
       </c>
       <c r="S39">
-        <v>41.946903</v>
+        <v>41.946902999999999</v>
       </c>
       <c r="T39">
-        <v>2.976818</v>
+        <v>2.9768180000000002</v>
       </c>
       <c r="U39">
         <v>142</v>
@@ -3584,16 +3717,16 @@
         <v>3.74078</v>
       </c>
       <c r="W39">
-        <v>33.380282</v>
+        <v>33.380282000000001</v>
       </c>
       <c r="X39">
         <v>87</v>
       </c>
       <c r="Y39">
-        <v>54.482759</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25">
+        <v>54.482759000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -3622,7 +3755,7 @@
         <v>1.539617</v>
       </c>
       <c r="J40">
-        <v>40.60344828</v>
+        <v>40.603448280000002</v>
       </c>
       <c r="K40" t="s">
         <v>42</v>
@@ -3640,22 +3773,22 @@
         <v>5635</v>
       </c>
       <c r="P40">
-        <v>835.847382</v>
+        <v>835.84738200000004</v>
       </c>
       <c r="Q40">
         <v>161</v>
       </c>
       <c r="S40">
-        <v>29.254658</v>
+        <v>29.254657999999999</v>
       </c>
       <c r="T40">
-        <v>2.857143</v>
+        <v>2.8571430000000002</v>
       </c>
       <c r="U40">
         <v>193</v>
       </c>
       <c r="V40">
-        <v>3.425022</v>
+        <v>3.4250219999999998</v>
       </c>
       <c r="W40">
         <v>24.404145</v>
@@ -3667,7 +3800,7 @@
         <v>40.603448</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -3693,10 +3826,10 @@
         <v>2411</v>
       </c>
       <c r="I41">
-        <v>1.352966</v>
+        <v>1.3529659999999999</v>
       </c>
       <c r="J41">
-        <v>57.975</v>
+        <v>57.975000000000001</v>
       </c>
       <c r="K41" t="s">
         <v>42</v>
@@ -3720,28 +3853,28 @@
         <v>95</v>
       </c>
       <c r="S41">
-        <v>48.821053</v>
+        <v>48.821052999999999</v>
       </c>
       <c r="T41">
-        <v>2.912324</v>
+        <v>2.9123239999999999</v>
       </c>
       <c r="U41">
         <v>104</v>
       </c>
       <c r="V41">
-        <v>3.188228</v>
+        <v>3.1882280000000001</v>
       </c>
       <c r="W41">
-        <v>44.596154</v>
+        <v>44.596153999999999</v>
       </c>
       <c r="X41">
         <v>80</v>
       </c>
       <c r="Y41">
-        <v>57.975</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25">
+        <v>57.975000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -3767,7 +3900,7 @@
         <v>2467</v>
       </c>
       <c r="I42">
-        <v>1.449939</v>
+        <v>1.4499390000000001</v>
       </c>
       <c r="J42">
         <v>14.12755102</v>
@@ -3788,7 +3921,7 @@
         <v>3577</v>
       </c>
       <c r="P42">
-        <v>774.112385</v>
+        <v>774.11238500000002</v>
       </c>
       <c r="Q42">
         <v>265</v>
@@ -3797,16 +3930,16 @@
         <v>10.449057</v>
       </c>
       <c r="T42">
-        <v>7.408443</v>
+        <v>7.4084430000000001</v>
       </c>
       <c r="U42">
         <v>282</v>
       </c>
       <c r="V42">
-        <v>7.883701</v>
+        <v>7.8837010000000003</v>
       </c>
       <c r="W42">
-        <v>9.819149</v>
+        <v>9.8191489999999995</v>
       </c>
       <c r="X42">
         <v>196</v>
@@ -3815,7 +3948,7 @@
         <v>14.127551</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -3844,7 +3977,7 @@
         <v>1.361399</v>
       </c>
       <c r="J43">
-        <v>20.44117647</v>
+        <v>20.441176469999998</v>
       </c>
       <c r="K43" t="s">
         <v>42</v>
@@ -3862,7 +3995,7 @@
         <v>3816</v>
       </c>
       <c r="P43">
-        <v>728.51153</v>
+        <v>728.51152999999999</v>
       </c>
       <c r="Q43">
         <v>191</v>
@@ -3871,13 +4004,13 @@
         <v>14.554974</v>
       </c>
       <c r="T43">
-        <v>5.005241</v>
+        <v>5.0052409999999998</v>
       </c>
       <c r="U43">
         <v>235</v>
       </c>
       <c r="V43">
-        <v>6.158281</v>
+        <v>6.1582809999999997</v>
       </c>
       <c r="W43">
         <v>11.829787</v>
@@ -3886,10 +4019,10 @@
         <v>136</v>
       </c>
       <c r="Y43">
-        <v>20.441176</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25">
+        <v>20.441175999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -3915,7 +4048,7 @@
         <v>1763</v>
       </c>
       <c r="I44">
-        <v>1.415769</v>
+        <v>1.4157690000000001</v>
       </c>
       <c r="J44">
         <v>42.6</v>
@@ -3942,19 +4075,19 @@
         <v>94</v>
       </c>
       <c r="S44">
-        <v>29.457447</v>
+        <v>29.457446999999998</v>
       </c>
       <c r="T44">
-        <v>3.766026</v>
+        <v>3.7660260000000001</v>
       </c>
       <c r="U44">
         <v>110</v>
       </c>
       <c r="V44">
-        <v>4.407051</v>
+        <v>4.4070510000000001</v>
       </c>
       <c r="W44">
-        <v>25.172727</v>
+        <v>25.172726999999998</v>
       </c>
       <c r="X44">
         <v>65</v>
@@ -3963,7 +4096,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -3989,7 +4122,7 @@
         <v>359</v>
       </c>
       <c r="I45">
-        <v>1.058496</v>
+        <v>1.0584960000000001</v>
       </c>
       <c r="J45">
         <v>116.8</v>
@@ -4010,7 +4143,7 @@
         <v>380</v>
       </c>
       <c r="P45">
-        <v>1536.842105</v>
+        <v>1536.8421049999999</v>
       </c>
       <c r="Q45">
         <v>8</v>
@@ -4019,16 +4152,16 @@
         <v>73</v>
       </c>
       <c r="T45">
-        <v>2.105263</v>
+        <v>2.1052629999999999</v>
       </c>
       <c r="U45">
         <v>9</v>
       </c>
       <c r="V45">
-        <v>2.368421</v>
+        <v>2.3684210000000001</v>
       </c>
       <c r="W45">
-        <v>64.888889</v>
+        <v>64.888889000000006</v>
       </c>
       <c r="X45">
         <v>5</v>
@@ -4037,7 +4170,7 @@
         <v>116.8</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>25</v>
       </c>
@@ -4063,7 +4196,7 @@
         <v>2082</v>
       </c>
       <c r="I46">
-        <v>1.477426</v>
+        <v>1.4774259999999999</v>
       </c>
       <c r="J46">
         <v>27.21</v>
@@ -4084,16 +4217,16 @@
         <v>3076</v>
       </c>
       <c r="P46">
-        <v>884.590377</v>
+        <v>884.59037699999999</v>
       </c>
       <c r="Q46">
         <v>143</v>
       </c>
       <c r="S46">
-        <v>19.027972</v>
+        <v>19.027971999999998</v>
       </c>
       <c r="T46">
-        <v>4.648895</v>
+        <v>4.6488950000000004</v>
       </c>
       <c r="U46">
         <v>165</v>
@@ -4102,7 +4235,7 @@
         <v>5.364109</v>
       </c>
       <c r="W46">
-        <v>16.490909</v>
+        <v>16.490908999999998</v>
       </c>
       <c r="X46">
         <v>100</v>
@@ -4111,7 +4244,7 @@
         <v>27.21</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -4137,7 +4270,7 @@
         <v>1432</v>
       </c>
       <c r="I47">
-        <v>1.518156</v>
+        <v>1.5181560000000001</v>
       </c>
       <c r="J47">
         <v>22.68333333</v>
@@ -4164,7 +4297,7 @@
         <v>157</v>
       </c>
       <c r="S47">
-        <v>17.33758</v>
+        <v>17.337579999999999</v>
       </c>
       <c r="T47">
         <v>7.221711</v>
@@ -4176,16 +4309,16 @@
         <v>7.313707</v>
       </c>
       <c r="W47">
-        <v>17.119497</v>
+        <v>17.119496999999999</v>
       </c>
       <c r="X47">
         <v>120</v>
       </c>
       <c r="Y47">
-        <v>22.683333</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25">
+        <v>22.683333000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>25</v>
       </c>
@@ -4211,10 +4344,10 @@
         <v>1436</v>
       </c>
       <c r="I48">
-        <v>1.574513</v>
+        <v>1.5745130000000001</v>
       </c>
       <c r="J48">
-        <v>42.21538462</v>
+        <v>42.215384620000002</v>
       </c>
       <c r="K48" t="s">
         <v>42</v>
@@ -4232,34 +4365,34 @@
         <v>2261</v>
       </c>
       <c r="P48">
-        <v>1213.622291</v>
+        <v>1213.6222909999999</v>
       </c>
       <c r="Q48">
         <v>81</v>
       </c>
       <c r="S48">
-        <v>33.876543</v>
+        <v>33.876542999999998</v>
       </c>
       <c r="T48">
-        <v>3.582486</v>
+        <v>3.5824859999999998</v>
       </c>
       <c r="U48">
         <v>84</v>
       </c>
       <c r="V48">
-        <v>3.71517</v>
+        <v>3.7151700000000001</v>
       </c>
       <c r="W48">
-        <v>32.666667</v>
+        <v>32.666666999999997</v>
       </c>
       <c r="X48">
         <v>65</v>
       </c>
       <c r="Y48">
-        <v>42.215385</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25">
+        <v>42.215384999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -4306,22 +4439,22 @@
         <v>2668</v>
       </c>
       <c r="P49">
-        <v>975.262369</v>
+        <v>975.26236900000004</v>
       </c>
       <c r="Q49">
         <v>222</v>
       </c>
       <c r="S49">
-        <v>11.720721</v>
+        <v>11.720720999999999</v>
       </c>
       <c r="T49">
-        <v>8.32084</v>
+        <v>8.3208400000000005</v>
       </c>
       <c r="U49">
         <v>251</v>
       </c>
       <c r="V49">
-        <v>9.407796</v>
+        <v>9.4077959999999994</v>
       </c>
       <c r="W49">
         <v>10.366534</v>
@@ -4333,7 +4466,7 @@
         <v>15.488095</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -4380,7 +4513,7 @@
         <v>1909</v>
       </c>
       <c r="P50">
-        <v>1387.637507</v>
+        <v>1387.6375069999999</v>
       </c>
       <c r="Q50">
         <v>32</v>
@@ -4389,16 +4522,16 @@
         <v>82.78125</v>
       </c>
       <c r="T50">
-        <v>1.67627</v>
+        <v>1.6762699999999999</v>
       </c>
       <c r="U50">
         <v>46</v>
       </c>
       <c r="V50">
-        <v>2.409639</v>
+        <v>2.4096389999999999</v>
       </c>
       <c r="W50">
-        <v>57.586957</v>
+        <v>57.586956999999998</v>
       </c>
       <c r="X50">
         <v>30</v>
@@ -4407,7 +4540,7 @@
         <v>88.3</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -4433,7 +4566,7 @@
         <v>730</v>
       </c>
       <c r="I51">
-        <v>1.265753</v>
+        <v>1.2657529999999999</v>
       </c>
       <c r="J51">
         <v>167</v>
@@ -4454,7 +4587,7 @@
         <v>924</v>
       </c>
       <c r="P51">
-        <v>1084.415584</v>
+        <v>1084.4155840000001</v>
       </c>
       <c r="Q51">
         <v>8</v>
@@ -4463,13 +4596,13 @@
         <v>125.25</v>
       </c>
       <c r="T51">
-        <v>0.865801</v>
+        <v>0.86580100000000004</v>
       </c>
       <c r="U51">
         <v>12</v>
       </c>
       <c r="V51">
-        <v>1.298701</v>
+        <v>1.2987010000000001</v>
       </c>
       <c r="W51">
         <v>83.5</v>
@@ -4481,7 +4614,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -4531,7 +4664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -4581,7 +4714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -4631,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -4681,7 +4814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -4707,10 +4840,10 @@
         <v>672</v>
       </c>
       <c r="I56">
-        <v>1.123512</v>
+        <v>1.1235120000000001</v>
       </c>
       <c r="J56">
-        <v>77.14285714</v>
+        <v>77.142857140000004</v>
       </c>
       <c r="K56" t="s">
         <v>42</v>
@@ -4728,34 +4861,34 @@
         <v>755</v>
       </c>
       <c r="P56">
-        <v>1430.463576</v>
+        <v>1430.4635760000001</v>
       </c>
       <c r="Q56">
         <v>21</v>
       </c>
       <c r="S56">
-        <v>51.428571</v>
+        <v>51.428570999999998</v>
       </c>
       <c r="T56">
-        <v>2.781457</v>
+        <v>2.7814570000000001</v>
       </c>
       <c r="U56">
         <v>21</v>
       </c>
       <c r="V56">
-        <v>2.781457</v>
+        <v>2.7814570000000001</v>
       </c>
       <c r="W56">
-        <v>51.428571</v>
+        <v>51.428570999999998</v>
       </c>
       <c r="X56">
         <v>14</v>
       </c>
       <c r="Y56">
-        <v>77.142857</v>
-      </c>
-    </row>
-    <row r="57" spans="1:25">
+        <v>77.142857000000006</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -4781,10 +4914,10 @@
         <v>599</v>
       </c>
       <c r="I57">
-        <v>1.075125</v>
+        <v>1.0751250000000001</v>
       </c>
       <c r="J57">
-        <v>89.45454545</v>
+        <v>89.454545449999998</v>
       </c>
       <c r="K57" t="s">
         <v>42</v>
@@ -4802,22 +4935,22 @@
         <v>644</v>
       </c>
       <c r="P57">
-        <v>1527.950311</v>
+        <v>1527.9503110000001</v>
       </c>
       <c r="Q57">
         <v>14</v>
       </c>
       <c r="S57">
-        <v>70.285714</v>
+        <v>70.285713999999999</v>
       </c>
       <c r="T57">
-        <v>2.173913</v>
+        <v>2.1739130000000002</v>
       </c>
       <c r="U57">
         <v>20</v>
       </c>
       <c r="V57">
-        <v>3.10559</v>
+        <v>3.1055899999999999</v>
       </c>
       <c r="W57">
         <v>49.2</v>
@@ -4826,10 +4959,10 @@
         <v>11</v>
       </c>
       <c r="Y57">
-        <v>89.454545</v>
-      </c>
-    </row>
-    <row r="58" spans="1:25">
+        <v>89.454544999999996</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -4858,7 +4991,7 @@
         <v>1.110398</v>
       </c>
       <c r="J58">
-        <v>59.36842105</v>
+        <v>59.368421050000002</v>
       </c>
       <c r="K58" t="s">
         <v>42</v>
@@ -4885,13 +5018,13 @@
         <v>45.12</v>
       </c>
       <c r="T58">
-        <v>2.890173</v>
+        <v>2.8901729999999999</v>
       </c>
       <c r="U58">
         <v>29</v>
       </c>
       <c r="V58">
-        <v>3.352601</v>
+        <v>3.3526009999999999</v>
       </c>
       <c r="W58">
         <v>38.896552</v>
@@ -4900,21 +5033,2138 @@
         <v>19</v>
       </c>
       <c r="Y58">
-        <v>59.368421</v>
+        <v>59.368420999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" t="s">
+        <v>162</v>
+      </c>
+      <c r="D59" t="s">
+        <v>28</v>
+      </c>
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59">
+        <v>57</v>
+      </c>
+      <c r="G59" t="s">
+        <v>41</v>
+      </c>
+      <c r="H59">
+        <v>2276</v>
+      </c>
+      <c r="I59">
+        <v>1.9244289999999999</v>
+      </c>
+      <c r="J59">
+        <v>96.701754390000005</v>
+      </c>
+      <c r="K59" t="s">
+        <v>42</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>5512</v>
+      </c>
+      <c r="N59" t="s">
+        <v>57</v>
+      </c>
+      <c r="O59">
+        <v>4380</v>
+      </c>
+      <c r="P59">
+        <v>1258.4474889999999</v>
+      </c>
+      <c r="Q59">
+        <v>100</v>
+      </c>
+      <c r="S59">
+        <v>55.12</v>
+      </c>
+      <c r="T59">
+        <v>2.2831049999999999</v>
+      </c>
+      <c r="U59">
+        <v>118</v>
+      </c>
+      <c r="V59">
+        <v>2.694064</v>
+      </c>
+      <c r="W59">
+        <v>46.711863999999998</v>
+      </c>
+      <c r="X59">
+        <v>57</v>
+      </c>
+      <c r="Y59">
+        <v>96.701753999999994</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
+        <v>161</v>
+      </c>
+      <c r="D60" t="s">
+        <v>121</v>
+      </c>
+      <c r="E60" t="s">
+        <v>29</v>
+      </c>
+      <c r="F60">
+        <v>136</v>
+      </c>
+      <c r="G60" t="s">
+        <v>30</v>
+      </c>
+      <c r="H60">
+        <v>2030</v>
+      </c>
+      <c r="I60">
+        <v>1.2581279999999999</v>
+      </c>
+      <c r="J60">
+        <v>28</v>
+      </c>
+      <c r="K60" t="s">
+        <v>42</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>3808</v>
+      </c>
+      <c r="N60" t="s">
+        <v>160</v>
+      </c>
+      <c r="O60">
+        <v>2554</v>
+      </c>
+      <c r="P60">
+        <v>1490.994518</v>
+      </c>
+      <c r="Q60">
+        <v>136</v>
+      </c>
+      <c r="S60">
+        <v>28</v>
+      </c>
+      <c r="T60">
+        <v>5.32498</v>
+      </c>
+      <c r="U60">
+        <v>136</v>
+      </c>
+      <c r="V60">
+        <v>5.32498</v>
+      </c>
+      <c r="W60">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" t="s">
+        <v>159</v>
+      </c>
+      <c r="D61" t="s">
+        <v>121</v>
+      </c>
+      <c r="E61" t="s">
+        <v>29</v>
+      </c>
+      <c r="F61">
+        <v>60</v>
+      </c>
+      <c r="G61" t="s">
+        <v>41</v>
+      </c>
+      <c r="H61">
+        <v>2170</v>
+      </c>
+      <c r="I61">
+        <v>1.5267280000000001</v>
+      </c>
+      <c r="J61">
+        <v>83.566666670000004</v>
+      </c>
+      <c r="K61" t="s">
+        <v>42</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>5014</v>
+      </c>
+      <c r="N61" t="s">
+        <v>155</v>
+      </c>
+      <c r="O61">
+        <v>3313</v>
+      </c>
+      <c r="P61">
+        <v>1513.4319350000001</v>
+      </c>
+      <c r="Q61">
+        <v>75</v>
+      </c>
+      <c r="S61">
+        <v>66.853333000000006</v>
+      </c>
+      <c r="T61">
+        <v>2.2638090000000002</v>
+      </c>
+      <c r="U61">
+        <v>79</v>
+      </c>
+      <c r="V61">
+        <v>2.3845459999999998</v>
+      </c>
+      <c r="W61">
+        <v>63.468353999999998</v>
+      </c>
+      <c r="X61">
+        <v>60</v>
+      </c>
+      <c r="Y61">
+        <v>83.566666999999995</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
+        <v>158</v>
+      </c>
+      <c r="D62" t="s">
+        <v>121</v>
+      </c>
+      <c r="E62" t="s">
+        <v>29</v>
+      </c>
+      <c r="F62">
+        <v>99</v>
+      </c>
+      <c r="G62" t="s">
+        <v>30</v>
+      </c>
+      <c r="H62">
+        <v>3187</v>
+      </c>
+      <c r="I62">
+        <v>1.8390340000000001</v>
+      </c>
+      <c r="J62">
+        <v>43.585858590000001</v>
+      </c>
+      <c r="K62" t="s">
+        <v>42</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>4315</v>
+      </c>
+      <c r="N62" t="s">
+        <v>145</v>
+      </c>
+      <c r="O62">
+        <v>5861</v>
+      </c>
+      <c r="P62">
+        <v>736.222488</v>
+      </c>
+      <c r="Q62">
+        <v>99</v>
+      </c>
+      <c r="S62">
+        <v>43.585858999999999</v>
+      </c>
+      <c r="T62">
+        <v>1.6891320000000001</v>
+      </c>
+      <c r="U62">
+        <v>101</v>
+      </c>
+      <c r="V62">
+        <v>1.723255</v>
+      </c>
+      <c r="W62">
+        <v>42.722771999999999</v>
+      </c>
+      <c r="X62">
+        <v>65</v>
+      </c>
+      <c r="Y62">
+        <v>66.384614999999997</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>157</v>
+      </c>
+      <c r="D63" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" t="s">
+        <v>29</v>
+      </c>
+      <c r="F63">
+        <v>73</v>
+      </c>
+      <c r="G63" t="s">
+        <v>41</v>
+      </c>
+      <c r="H63">
+        <v>1920</v>
+      </c>
+      <c r="I63">
+        <v>1.5020830000000001</v>
+      </c>
+      <c r="J63">
+        <v>90.821917810000002</v>
+      </c>
+      <c r="K63" t="s">
+        <v>42</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>6630</v>
+      </c>
+      <c r="N63" t="s">
+        <v>65</v>
+      </c>
+      <c r="O63">
+        <v>2884</v>
+      </c>
+      <c r="P63">
+        <v>2298.8904299999999</v>
+      </c>
+      <c r="Q63">
+        <v>126</v>
+      </c>
+      <c r="S63">
+        <v>52.619047999999999</v>
+      </c>
+      <c r="T63">
+        <v>4.368932</v>
+      </c>
+      <c r="U63">
+        <v>127</v>
+      </c>
+      <c r="V63">
+        <v>4.4036059999999999</v>
+      </c>
+      <c r="W63">
+        <v>52.204723999999999</v>
+      </c>
+      <c r="X63">
+        <v>73</v>
+      </c>
+      <c r="Y63">
+        <v>90.821917999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" t="s">
+        <v>156</v>
+      </c>
+      <c r="D64" t="s">
+        <v>45</v>
+      </c>
+      <c r="E64" t="s">
+        <v>29</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="K64" t="s">
+        <v>42</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64" t="s">
+        <v>155</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
+        <v>154</v>
+      </c>
+      <c r="D65" t="s">
+        <v>28</v>
+      </c>
+      <c r="E65" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65">
+        <v>95</v>
+      </c>
+      <c r="G65" t="s">
+        <v>41</v>
+      </c>
+      <c r="H65">
+        <v>2460</v>
+      </c>
+      <c r="I65">
+        <v>1.4621949999999999</v>
+      </c>
+      <c r="J65">
+        <v>60.389473680000002</v>
+      </c>
+      <c r="K65" t="s">
+        <v>42</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>5737</v>
+      </c>
+      <c r="N65" t="s">
+        <v>63</v>
+      </c>
+      <c r="O65">
+        <v>3597</v>
+      </c>
+      <c r="P65">
+        <v>1594.9402279999999</v>
+      </c>
+      <c r="Q65">
+        <v>115</v>
+      </c>
+      <c r="S65">
+        <v>49.886957000000002</v>
+      </c>
+      <c r="T65">
+        <v>3.1971090000000002</v>
+      </c>
+      <c r="U65">
+        <v>125</v>
+      </c>
+      <c r="V65">
+        <v>3.4751180000000002</v>
+      </c>
+      <c r="W65">
+        <v>45.896000000000001</v>
+      </c>
+      <c r="X65">
+        <v>95</v>
+      </c>
+      <c r="Y65">
+        <v>60.389474</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" t="s">
+        <v>153</v>
+      </c>
+      <c r="D66" t="s">
+        <v>28</v>
+      </c>
+      <c r="E66" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66">
+        <v>471</v>
+      </c>
+      <c r="G66" t="s">
+        <v>41</v>
+      </c>
+      <c r="H66">
+        <v>9187</v>
+      </c>
+      <c r="I66">
+        <v>1.4212469999999999</v>
+      </c>
+      <c r="J66">
+        <v>45.195329090000001</v>
+      </c>
+      <c r="K66" t="s">
+        <v>42</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>21287</v>
+      </c>
+      <c r="N66" t="s">
+        <v>152</v>
+      </c>
+      <c r="O66">
+        <v>13057</v>
+      </c>
+      <c r="P66">
+        <v>1630.3132419999999</v>
+      </c>
+      <c r="Q66">
+        <v>735</v>
+      </c>
+      <c r="S66">
+        <v>28.961905000000002</v>
+      </c>
+      <c r="T66">
+        <v>5.6291640000000003</v>
+      </c>
+      <c r="U66">
+        <v>769</v>
+      </c>
+      <c r="V66">
+        <v>5.8895609999999996</v>
+      </c>
+      <c r="W66">
+        <v>27.681404000000001</v>
+      </c>
+      <c r="X66">
+        <v>471</v>
+      </c>
+      <c r="Y66">
+        <v>45.195329000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>151</v>
+      </c>
+      <c r="D67" t="s">
+        <v>45</v>
+      </c>
+      <c r="E67" t="s">
+        <v>29</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="K67" t="s">
+        <v>42</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67" t="s">
+        <v>119</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D68" t="s">
+        <v>28</v>
+      </c>
+      <c r="E68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F68">
+        <v>131</v>
+      </c>
+      <c r="G68" t="s">
+        <v>41</v>
+      </c>
+      <c r="H68">
+        <v>3555</v>
+      </c>
+      <c r="I68">
+        <v>1.720113</v>
+      </c>
+      <c r="J68">
+        <v>37.923664119999998</v>
+      </c>
+      <c r="K68" t="s">
+        <v>42</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>4968</v>
+      </c>
+      <c r="N68" t="s">
+        <v>149</v>
+      </c>
+      <c r="O68">
+        <v>6115</v>
+      </c>
+      <c r="P68">
+        <v>812.42845499999999</v>
+      </c>
+      <c r="Q68">
+        <v>207</v>
+      </c>
+      <c r="S68">
+        <v>24</v>
+      </c>
+      <c r="T68">
+        <v>3.385119</v>
+      </c>
+      <c r="U68">
+        <v>210</v>
+      </c>
+      <c r="V68">
+        <v>3.4341780000000002</v>
+      </c>
+      <c r="W68">
+        <v>23.657143000000001</v>
+      </c>
+      <c r="X68">
+        <v>131</v>
+      </c>
+      <c r="Y68">
+        <v>37.923664000000002</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>148</v>
+      </c>
+      <c r="D69" t="s">
+        <v>28</v>
+      </c>
+      <c r="E69" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69">
+        <v>105</v>
+      </c>
+      <c r="G69" t="s">
+        <v>30</v>
+      </c>
+      <c r="H69">
+        <v>4090</v>
+      </c>
+      <c r="I69">
+        <v>1.556235</v>
+      </c>
+      <c r="J69">
+        <v>48.628571430000001</v>
+      </c>
+      <c r="K69" t="s">
+        <v>42</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>5106</v>
+      </c>
+      <c r="N69" t="s">
+        <v>147</v>
+      </c>
+      <c r="O69">
+        <v>6365</v>
+      </c>
+      <c r="P69">
+        <v>802.19952899999998</v>
+      </c>
+      <c r="Q69">
+        <v>105</v>
+      </c>
+      <c r="S69">
+        <v>48.628571000000001</v>
+      </c>
+      <c r="T69">
+        <v>1.6496470000000001</v>
+      </c>
+      <c r="U69">
+        <v>126</v>
+      </c>
+      <c r="V69">
+        <v>1.979576</v>
+      </c>
+      <c r="W69">
+        <v>40.523809999999997</v>
+      </c>
+      <c r="X69">
+        <v>72</v>
+      </c>
+      <c r="Y69">
+        <v>70.916667000000004</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>146</v>
+      </c>
+      <c r="D70" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70">
+        <v>176</v>
+      </c>
+      <c r="G70" t="s">
+        <v>30</v>
+      </c>
+      <c r="H70">
+        <v>2144</v>
+      </c>
+      <c r="I70">
+        <v>1.288713</v>
+      </c>
+      <c r="J70">
+        <v>24.125</v>
+      </c>
+      <c r="K70" t="s">
+        <v>42</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>4246</v>
+      </c>
+      <c r="N70" t="s">
+        <v>145</v>
+      </c>
+      <c r="O70">
+        <v>2763</v>
+      </c>
+      <c r="P70">
+        <v>1536.7354330000001</v>
+      </c>
+      <c r="Q70">
+        <v>176</v>
+      </c>
+      <c r="S70">
+        <v>24.125</v>
+      </c>
+      <c r="T70">
+        <v>6.3698880000000004</v>
+      </c>
+      <c r="U70">
+        <v>181</v>
+      </c>
+      <c r="V70">
+        <v>6.5508509999999998</v>
+      </c>
+      <c r="W70">
+        <v>23.458563999999999</v>
+      </c>
+      <c r="X70">
+        <v>110</v>
+      </c>
+      <c r="Y70">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>144</v>
+      </c>
+      <c r="D71" t="s">
+        <v>121</v>
+      </c>
+      <c r="E71" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71">
+        <v>155</v>
+      </c>
+      <c r="G71" t="s">
+        <v>30</v>
+      </c>
+      <c r="H71">
+        <v>2301</v>
+      </c>
+      <c r="I71">
+        <v>1.3311599999999999</v>
+      </c>
+      <c r="J71">
+        <v>26.716129030000001</v>
+      </c>
+      <c r="K71" t="s">
+        <v>42</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>4141</v>
+      </c>
+      <c r="N71" t="s">
+        <v>132</v>
+      </c>
+      <c r="O71">
+        <v>3063</v>
+      </c>
+      <c r="P71">
+        <v>1351.94254</v>
+      </c>
+      <c r="Q71">
+        <v>155</v>
+      </c>
+      <c r="S71">
+        <v>26.716128999999999</v>
+      </c>
+      <c r="T71">
+        <v>5.0603980000000002</v>
+      </c>
+      <c r="U71">
+        <v>162</v>
+      </c>
+      <c r="V71">
+        <v>5.288932</v>
+      </c>
+      <c r="W71">
+        <v>25.561727999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
+        <v>143</v>
+      </c>
+      <c r="D72" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72" t="s">
+        <v>29</v>
+      </c>
+      <c r="F72">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s">
+        <v>30</v>
+      </c>
+      <c r="H72">
+        <v>2879</v>
+      </c>
+      <c r="I72">
+        <v>1.478291</v>
+      </c>
+      <c r="J72">
+        <v>62.6875</v>
+      </c>
+      <c r="K72" t="s">
+        <v>42</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>5015</v>
+      </c>
+      <c r="N72" t="s">
+        <v>142</v>
+      </c>
+      <c r="O72">
+        <v>4256</v>
+      </c>
+      <c r="P72">
+        <v>1178.336466</v>
+      </c>
+      <c r="Q72">
+        <v>80</v>
+      </c>
+      <c r="S72">
+        <v>62.6875</v>
+      </c>
+      <c r="T72">
+        <v>1.879699</v>
+      </c>
+      <c r="U72">
+        <v>83</v>
+      </c>
+      <c r="V72">
+        <v>1.950188</v>
+      </c>
+      <c r="W72">
+        <v>60.421686999999999</v>
+      </c>
+      <c r="X72">
+        <v>53</v>
+      </c>
+      <c r="Y72">
+        <v>94.622641999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" t="s">
+        <v>121</v>
+      </c>
+      <c r="E73" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73">
+        <v>235</v>
+      </c>
+      <c r="G73" t="s">
+        <v>30</v>
+      </c>
+      <c r="H73">
+        <v>2807</v>
+      </c>
+      <c r="I73">
+        <v>1.2087639999999999</v>
+      </c>
+      <c r="J73">
+        <v>17.268085110000001</v>
+      </c>
+      <c r="K73" t="s">
+        <v>42</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>4058</v>
+      </c>
+      <c r="N73" t="s">
+        <v>123</v>
+      </c>
+      <c r="O73">
+        <v>3393</v>
+      </c>
+      <c r="P73">
+        <v>1195.9917479999999</v>
+      </c>
+      <c r="Q73">
+        <v>235</v>
+      </c>
+      <c r="S73">
+        <v>17.268084999999999</v>
+      </c>
+      <c r="T73">
+        <v>6.926024</v>
+      </c>
+      <c r="U73">
+        <v>239</v>
+      </c>
+      <c r="V73">
+        <v>7.043914</v>
+      </c>
+      <c r="W73">
+        <v>16.97908</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" t="s">
+        <v>140</v>
+      </c>
+      <c r="D74" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74">
+        <v>360</v>
+      </c>
+      <c r="G74" t="s">
+        <v>30</v>
+      </c>
+      <c r="H74">
+        <v>3158</v>
+      </c>
+      <c r="I74">
+        <v>1.5250159999999999</v>
+      </c>
+      <c r="J74">
+        <v>13.355555560000001</v>
+      </c>
+      <c r="K74" t="s">
+        <v>42</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>4808</v>
+      </c>
+      <c r="N74" t="s">
+        <v>139</v>
+      </c>
+      <c r="O74">
+        <v>4816</v>
+      </c>
+      <c r="P74">
+        <v>998.33887000000004</v>
+      </c>
+      <c r="Q74">
+        <v>360</v>
+      </c>
+      <c r="S74">
+        <v>13.355556</v>
+      </c>
+      <c r="T74">
+        <v>7.4750829999999997</v>
+      </c>
+      <c r="U74">
+        <v>362</v>
+      </c>
+      <c r="V74">
+        <v>7.5166110000000002</v>
+      </c>
+      <c r="W74">
+        <v>13.281768</v>
+      </c>
+      <c r="X74">
+        <v>245</v>
+      </c>
+      <c r="Y74">
+        <v>19.624490000000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" t="s">
+        <v>138</v>
+      </c>
+      <c r="D75" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75">
+        <v>256</v>
+      </c>
+      <c r="G75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H75">
+        <v>4837</v>
+      </c>
+      <c r="I75">
+        <v>1.645235</v>
+      </c>
+      <c r="J75">
+        <v>21.64453125</v>
+      </c>
+      <c r="K75" t="s">
+        <v>42</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>5541</v>
+      </c>
+      <c r="N75" t="s">
+        <v>74</v>
+      </c>
+      <c r="O75">
+        <v>7958</v>
+      </c>
+      <c r="P75">
+        <v>696.28047200000003</v>
+      </c>
+      <c r="Q75">
+        <v>359</v>
+      </c>
+      <c r="S75">
+        <v>15.43454</v>
+      </c>
+      <c r="T75">
+        <v>4.5111840000000001</v>
+      </c>
+      <c r="U75">
+        <v>447</v>
+      </c>
+      <c r="V75">
+        <v>5.6169890000000002</v>
+      </c>
+      <c r="W75">
+        <v>12.395973</v>
+      </c>
+      <c r="X75">
+        <v>256</v>
+      </c>
+      <c r="Y75">
+        <v>21.644531000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>137</v>
+      </c>
+      <c r="D76" t="s">
+        <v>121</v>
+      </c>
+      <c r="E76" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76">
+        <v>147</v>
+      </c>
+      <c r="G76" t="s">
+        <v>30</v>
+      </c>
+      <c r="H76">
+        <v>2431</v>
+      </c>
+      <c r="I76">
+        <v>1.4862200000000001</v>
+      </c>
+      <c r="J76">
+        <v>28.53061224</v>
+      </c>
+      <c r="K76" t="s">
+        <v>42</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>4194</v>
+      </c>
+      <c r="N76" t="s">
+        <v>132</v>
+      </c>
+      <c r="O76">
+        <v>3613</v>
+      </c>
+      <c r="P76">
+        <v>1160.8081930000001</v>
+      </c>
+      <c r="Q76">
+        <v>147</v>
+      </c>
+      <c r="S76">
+        <v>28.530612000000001</v>
+      </c>
+      <c r="T76">
+        <v>4.0686410000000004</v>
+      </c>
+      <c r="U76">
+        <v>158</v>
+      </c>
+      <c r="V76">
+        <v>4.3730969999999996</v>
+      </c>
+      <c r="W76">
+        <v>26.544304</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" t="s">
+        <v>88</v>
+      </c>
+      <c r="D77" t="s">
+        <v>45</v>
+      </c>
+      <c r="E77" t="s">
+        <v>29</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="K77" t="s">
+        <v>42</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77" t="s">
+        <v>136</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" t="s">
+        <v>135</v>
+      </c>
+      <c r="D78" t="s">
+        <v>45</v>
+      </c>
+      <c r="E78" t="s">
+        <v>29</v>
+      </c>
+      <c r="F78">
+        <v>114</v>
+      </c>
+      <c r="G78" t="s">
+        <v>41</v>
+      </c>
+      <c r="H78">
+        <v>3595</v>
+      </c>
+      <c r="I78">
+        <v>1.50153</v>
+      </c>
+      <c r="J78">
+        <v>52.622807020000003</v>
+      </c>
+      <c r="K78" t="s">
+        <v>42</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>5999</v>
+      </c>
+      <c r="N78" t="s">
+        <v>78</v>
+      </c>
+      <c r="O78">
+        <v>5398</v>
+      </c>
+      <c r="P78">
+        <v>1111.337532</v>
+      </c>
+      <c r="Q78">
+        <v>165</v>
+      </c>
+      <c r="S78">
+        <v>36.357576000000002</v>
+      </c>
+      <c r="T78">
+        <v>3.0566879999999998</v>
+      </c>
+      <c r="U78">
+        <v>203</v>
+      </c>
+      <c r="V78">
+        <v>3.7606519999999999</v>
+      </c>
+      <c r="W78">
+        <v>29.551724</v>
+      </c>
+      <c r="X78">
+        <v>114</v>
+      </c>
+      <c r="Y78">
+        <v>52.622807000000002</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" t="s">
+        <v>134</v>
+      </c>
+      <c r="D79" t="s">
+        <v>121</v>
+      </c>
+      <c r="E79" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s">
+        <v>30</v>
+      </c>
+      <c r="H79">
+        <v>1189</v>
+      </c>
+      <c r="I79">
+        <v>3.3355760000000001</v>
+      </c>
+      <c r="J79">
+        <v>55.705128209999998</v>
+      </c>
+      <c r="K79" t="s">
+        <v>42</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>4345</v>
+      </c>
+      <c r="N79" t="s">
+        <v>110</v>
+      </c>
+      <c r="O79">
+        <v>3966</v>
+      </c>
+      <c r="P79">
+        <v>1095.562279</v>
+      </c>
+      <c r="Q79">
+        <v>78</v>
+      </c>
+      <c r="S79">
+        <v>55.705128000000002</v>
+      </c>
+      <c r="T79">
+        <v>1.966717</v>
+      </c>
+      <c r="U79">
+        <v>78</v>
+      </c>
+      <c r="V79">
+        <v>1.966717</v>
+      </c>
+      <c r="W79">
+        <v>55.705128000000002</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" t="s">
+        <v>133</v>
+      </c>
+      <c r="D80" t="s">
+        <v>121</v>
+      </c>
+      <c r="E80" t="s">
+        <v>29</v>
+      </c>
+      <c r="F80">
+        <v>128</v>
+      </c>
+      <c r="G80" t="s">
+        <v>30</v>
+      </c>
+      <c r="H80">
+        <v>2696</v>
+      </c>
+      <c r="I80">
+        <v>1.378709</v>
+      </c>
+      <c r="J80">
+        <v>31.0859375</v>
+      </c>
+      <c r="K80" t="s">
+        <v>42</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>3979</v>
+      </c>
+      <c r="N80" t="s">
+        <v>132</v>
+      </c>
+      <c r="O80">
+        <v>3717</v>
+      </c>
+      <c r="P80">
+        <v>1070.486952</v>
+      </c>
+      <c r="Q80">
+        <v>128</v>
+      </c>
+      <c r="S80">
+        <v>31.085937999999999</v>
+      </c>
+      <c r="T80">
+        <v>3.4436369999999998</v>
+      </c>
+      <c r="U80">
+        <v>138</v>
+      </c>
+      <c r="V80">
+        <v>3.712672</v>
+      </c>
+      <c r="W80">
+        <v>28.833333</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>25</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" t="s">
+        <v>131</v>
+      </c>
+      <c r="D81" t="s">
+        <v>28</v>
+      </c>
+      <c r="E81" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81">
+        <v>101</v>
+      </c>
+      <c r="G81" t="s">
+        <v>30</v>
+      </c>
+      <c r="H81">
+        <v>1677</v>
+      </c>
+      <c r="I81">
+        <v>1.443649</v>
+      </c>
+      <c r="J81">
+        <v>44.920792079999998</v>
+      </c>
+      <c r="K81" t="s">
+        <v>42</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>4537</v>
+      </c>
+      <c r="N81" t="s">
+        <v>130</v>
+      </c>
+      <c r="O81">
+        <v>2421</v>
+      </c>
+      <c r="P81">
+        <v>1874.019</v>
+      </c>
+      <c r="Q81">
+        <v>101</v>
+      </c>
+      <c r="S81">
+        <v>44.920791999999999</v>
+      </c>
+      <c r="T81">
+        <v>4.1718299999999999</v>
+      </c>
+      <c r="U81">
+        <v>104</v>
+      </c>
+      <c r="V81">
+        <v>4.2957460000000003</v>
+      </c>
+      <c r="W81">
+        <v>43.625</v>
+      </c>
+      <c r="X81">
+        <v>1</v>
+      </c>
+      <c r="Y81">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>129</v>
+      </c>
+      <c r="D82" t="s">
+        <v>121</v>
+      </c>
+      <c r="E82" t="s">
+        <v>29</v>
+      </c>
+      <c r="F82">
+        <v>64</v>
+      </c>
+      <c r="G82" t="s">
+        <v>30</v>
+      </c>
+      <c r="H82">
+        <v>2831</v>
+      </c>
+      <c r="I82">
+        <v>1.4641470000000001</v>
+      </c>
+      <c r="J82">
+        <v>67.53125</v>
+      </c>
+      <c r="K82" t="s">
+        <v>42</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>4322</v>
+      </c>
+      <c r="N82" t="s">
+        <v>128</v>
+      </c>
+      <c r="O82">
+        <v>4145</v>
+      </c>
+      <c r="P82">
+        <v>1042.702051</v>
+      </c>
+      <c r="Q82">
+        <v>64</v>
+      </c>
+      <c r="S82">
+        <v>67.53125</v>
+      </c>
+      <c r="T82">
+        <v>1.5440290000000001</v>
+      </c>
+      <c r="U82">
+        <v>71</v>
+      </c>
+      <c r="V82">
+        <v>1.712907</v>
+      </c>
+      <c r="W82">
+        <v>60.873238999999998</v>
+      </c>
+      <c r="X82">
+        <v>46</v>
+      </c>
+      <c r="Y82">
+        <v>93.956522000000007</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" t="s">
+        <v>127</v>
+      </c>
+      <c r="D83" t="s">
+        <v>45</v>
+      </c>
+      <c r="E83" t="s">
+        <v>29</v>
+      </c>
+      <c r="H83">
+        <v>20</v>
+      </c>
+      <c r="I83">
+        <v>1.05</v>
+      </c>
+      <c r="K83" t="s">
+        <v>42</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>15</v>
+      </c>
+      <c r="N83" t="s">
+        <v>126</v>
+      </c>
+      <c r="O83">
+        <v>21</v>
+      </c>
+      <c r="P83">
+        <v>714.28571399999998</v>
+      </c>
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" t="s">
+        <v>108</v>
+      </c>
+      <c r="D84" t="s">
+        <v>121</v>
+      </c>
+      <c r="E84" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84">
+        <v>68</v>
+      </c>
+      <c r="G84" t="s">
+        <v>30</v>
+      </c>
+      <c r="H84">
+        <v>1912</v>
+      </c>
+      <c r="I84">
+        <v>1.2165269999999999</v>
+      </c>
+      <c r="J84">
+        <v>57.544117649999997</v>
+      </c>
+      <c r="K84" t="s">
+        <v>42</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>3913</v>
+      </c>
+      <c r="N84" t="s">
+        <v>125</v>
+      </c>
+      <c r="O84">
+        <v>2326</v>
+      </c>
+      <c r="P84">
+        <v>1682.287188</v>
+      </c>
+      <c r="Q84">
+        <v>68</v>
+      </c>
+      <c r="S84">
+        <v>57.544117999999997</v>
+      </c>
+      <c r="T84">
+        <v>2.9234740000000001</v>
+      </c>
+      <c r="U84">
+        <v>71</v>
+      </c>
+      <c r="V84">
+        <v>3.052451</v>
+      </c>
+      <c r="W84">
+        <v>55.112676</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" t="s">
+        <v>124</v>
+      </c>
+      <c r="D85" t="s">
+        <v>121</v>
+      </c>
+      <c r="E85" t="s">
+        <v>29</v>
+      </c>
+      <c r="F85">
+        <v>63</v>
+      </c>
+      <c r="G85" t="s">
+        <v>30</v>
+      </c>
+      <c r="H85">
+        <v>1840</v>
+      </c>
+      <c r="I85">
+        <v>1.288043</v>
+      </c>
+      <c r="J85">
+        <v>65.095238100000003</v>
+      </c>
+      <c r="K85" t="s">
+        <v>42</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>4101</v>
+      </c>
+      <c r="N85" t="s">
+        <v>123</v>
+      </c>
+      <c r="O85">
+        <v>2370</v>
+      </c>
+      <c r="P85">
+        <v>1730.379747</v>
+      </c>
+      <c r="Q85">
+        <v>63</v>
+      </c>
+      <c r="S85">
+        <v>65.095237999999995</v>
+      </c>
+      <c r="T85">
+        <v>2.6582279999999998</v>
+      </c>
+      <c r="U85">
+        <v>69</v>
+      </c>
+      <c r="V85">
+        <v>2.9113920000000002</v>
+      </c>
+      <c r="W85">
+        <v>59.434783000000003</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
+        <v>122</v>
+      </c>
+      <c r="D86" t="s">
+        <v>121</v>
+      </c>
+      <c r="E86" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86">
+        <v>122</v>
+      </c>
+      <c r="G86" t="s">
+        <v>41</v>
+      </c>
+      <c r="H86">
+        <v>2815</v>
+      </c>
+      <c r="I86">
+        <v>1.280284</v>
+      </c>
+      <c r="J86">
+        <v>37.852459019999998</v>
+      </c>
+      <c r="K86" t="s">
+        <v>42</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>4618</v>
+      </c>
+      <c r="N86" t="s">
+        <v>119</v>
+      </c>
+      <c r="O86">
+        <v>3604</v>
+      </c>
+      <c r="P86">
+        <v>1281.354051</v>
+      </c>
+      <c r="Q86">
+        <v>134</v>
+      </c>
+      <c r="S86">
+        <v>34.462687000000003</v>
+      </c>
+      <c r="T86">
+        <v>3.7180909999999998</v>
+      </c>
+      <c r="U86">
+        <v>163</v>
+      </c>
+      <c r="V86">
+        <v>4.5227529999999998</v>
+      </c>
+      <c r="W86">
+        <v>28.331288000000001</v>
+      </c>
+      <c r="X86">
+        <v>122</v>
+      </c>
+      <c r="Y86">
+        <v>37.852459000000003</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" t="s">
+        <v>120</v>
+      </c>
+      <c r="D87" t="s">
+        <v>45</v>
+      </c>
+      <c r="E87" t="s">
+        <v>29</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="K87" t="s">
+        <v>42</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87" t="s">
+        <v>119</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="U87">
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" t="s">
+        <v>118</v>
+      </c>
+      <c r="D88" t="s">
+        <v>28</v>
+      </c>
+      <c r="E88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88">
+        <v>167</v>
+      </c>
+      <c r="G88" t="s">
+        <v>41</v>
+      </c>
+      <c r="H88">
+        <v>3893</v>
+      </c>
+      <c r="I88">
+        <v>1.825841</v>
+      </c>
+      <c r="J88">
+        <v>31.550898199999999</v>
+      </c>
+      <c r="K88" t="s">
+        <v>42</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>5269</v>
+      </c>
+      <c r="N88" t="s">
+        <v>65</v>
+      </c>
+      <c r="O88">
+        <v>7108</v>
+      </c>
+      <c r="P88">
+        <v>741.27743399999997</v>
+      </c>
+      <c r="Q88">
+        <v>178</v>
+      </c>
+      <c r="S88">
+        <v>29.601123999999999</v>
+      </c>
+      <c r="T88">
+        <v>2.5042209999999998</v>
+      </c>
+      <c r="U88">
+        <v>205</v>
+      </c>
+      <c r="V88">
+        <v>2.884074</v>
+      </c>
+      <c r="W88">
+        <v>25.702438999999998</v>
+      </c>
+      <c r="X88">
+        <v>167</v>
+      </c>
+      <c r="Y88">
+        <v>31.550898</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
+        <v>117</v>
+      </c>
+      <c r="D89" t="s">
+        <v>28</v>
+      </c>
+      <c r="E89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F89">
+        <v>68</v>
+      </c>
+      <c r="G89" t="s">
+        <v>41</v>
+      </c>
+      <c r="H89">
+        <v>2641</v>
+      </c>
+      <c r="I89">
+        <v>1.792503</v>
+      </c>
+      <c r="J89">
+        <v>89.382352940000004</v>
+      </c>
+      <c r="K89" t="s">
+        <v>42</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>6078</v>
+      </c>
+      <c r="N89" t="s">
+        <v>74</v>
+      </c>
+      <c r="O89">
+        <v>4734</v>
+      </c>
+      <c r="P89">
+        <v>1283.9036759999999</v>
+      </c>
+      <c r="Q89">
+        <v>107</v>
+      </c>
+      <c r="S89">
+        <v>56.803738000000003</v>
+      </c>
+      <c r="T89">
+        <v>2.2602449999999998</v>
+      </c>
+      <c r="U89">
+        <v>117</v>
+      </c>
+      <c r="V89">
+        <v>2.4714830000000001</v>
+      </c>
+      <c r="W89">
+        <v>51.948718</v>
+      </c>
+      <c r="X89">
+        <v>68</v>
+      </c>
+      <c r="Y89">
+        <v>89.382352999999995</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>